--- a/data/trans_orig/P41C_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Edad-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023</t>
+          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56501</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121503</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118452</t>
+          <t>117850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134189</t>
+          <t>134207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132866</t>
+          <t>132380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143342</t>
+          <t>143208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256026</t>
+          <t>257421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275673</t>
+          <t>275936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>864</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>178565</t>
+          <t>180442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192687</t>
+          <t>192671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198329</t>
+          <t>198156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209445</t>
+          <t>209659</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>383660</t>
+          <t>382705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>399808</t>
+          <t>400177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>817</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>426373</t>
+          <t>425531</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>453381</t>
+          <t>453647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>229929</t>
+          <t>229837</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239981</t>
+          <t>239524</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>662694</t>
+          <t>662226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>694078</t>
+          <t>693851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13434</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26843</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>65-74</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4130,107 +4130,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>564</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>852928</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>835387</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>869304</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>971</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>665842</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655196</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>673870</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1518768</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1499311</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1539506</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -4243,107 +4243,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -4356,107 +4356,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -4469,107 +4469,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4582,107 +4582,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20368</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34389</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -4695,1488 +4695,122 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>879419</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>879419</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>879419</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695279</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695279</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695279</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1574697</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1574697</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1574697</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Sí, ya lo intentamos anteriormente, aunque sin relaciones sexuales frecuentes (menos de 2 días a la semana, en promedio</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Sí, ya lo intentamos anteriormente con relaciones sexuales frecuentes (al menos 2 días a la semana, en promedio durante</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Sí, en la actualidad lo llevamos intentando, aunque sin relaciones sexuales frecuentes (menos de 2 días a la semana, en</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Sí, en la actualidad lo llevamos intentando con relaciones sexuales frecuentes (al menos 2 días a la semana, en promedio</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>852928</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>835103</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>868457</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>971</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>665842</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>655429</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>674208</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1535</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>1518768</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>1498957</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>1541807</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Sí, ya lo intentamos anteriormente, aunque sin relaciones sexuales frecuentes (menos de 2 días a la semana, en promedio</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>6119</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>3225</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>6941</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>4433</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>1565</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>9164</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Sí, ya lo intentamos anteriormente con relaciones sexuales frecuentes (al menos 2 días a la semana, en promedio durante</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>11975</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>4136</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>22527</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>14668</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>9073</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>21579</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>26643</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>15630</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>39247</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Sí, en la actualidad lo llevamos intentando, aunque sin relaciones sexuales frecuentes (menos de 2 días a la semana, en</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2761</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>11143</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>6580</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>4484</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>11274</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Sí, en la actualidad lo llevamos intentando con relaciones sexuales frecuentes (al menos 2 días a la semana, en promedio</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>10548</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>3449</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>23006</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>9821</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>4830</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>17091</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>20368</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>10278</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>33807</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>879419</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>879419</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>879419</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>695279</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>695279</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>695279</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>1574697</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>1574697</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>1574697</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A46:A51"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_orig/P41C_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>129812</t>
+          <t>144849</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117850</t>
+          <t>132357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134207</t>
+          <t>149805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>139660</t>
+          <t>155136</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132380</t>
+          <t>148953</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143208</t>
+          <t>159559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>269473</t>
+          <t>299985</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>257421</t>
+          <t>285338</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275936</t>
+          <t>306585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>885</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>135429</t>
+          <t>150997</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>135429</t>
+          <t>150997</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135429</t>
+          <t>150997</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>146428</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>146428</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>146428</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>281858</t>
+          <t>313865</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>281858</t>
+          <t>313865</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>281858</t>
+          <t>313865</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>187760</t>
+          <t>209484</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>180442</t>
+          <t>201327</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192671</t>
+          <t>214954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>204878</t>
+          <t>234414</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198156</t>
+          <t>227442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209659</t>
+          <t>239668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>392638</t>
+          <t>443898</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>382705</t>
+          <t>432824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>400177</t>
+          <t>451178</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>728</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>19268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>197602</t>
+          <t>220598</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>197602</t>
+          <t>220598</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>197602</t>
+          <t>220598</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>216785</t>
+          <t>247365</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>216785</t>
+          <t>247365</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>216785</t>
+          <t>247365</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>414387</t>
+          <t>467963</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>414387</t>
+          <t>467963</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>414387</t>
+          <t>467963</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>443985</t>
+          <t>219815</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>425531</t>
+          <t>211041</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>453647</t>
+          <t>225361</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>235407</t>
+          <t>257371</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>229837</t>
+          <t>251616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239524</t>
+          <t>261484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>679393</t>
+          <t>477185</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>662226</t>
+          <t>466600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>693851</t>
+          <t>484336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,92 +2894,92 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>6664</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>3789</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1137</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>9225</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2499</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>6227</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3545</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>9135</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,84 +3233,84 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2276</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6910</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>8463</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>455018</t>
+          <t>231108</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>455018</t>
+          <t>231108</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>455018</t>
+          <t>231108</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>246169</t>
+          <t>268457</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>246169</t>
+          <t>268457</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>246169</t>
+          <t>268457</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>701187</t>
+          <t>499565</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>701187</t>
+          <t>499565</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>701187</t>
+          <t>499565</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>852928</t>
+          <t>667199</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>835387</t>
+          <t>649949</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>869304</t>
+          <t>677410</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>665842</t>
+          <t>741827</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>655196</t>
+          <t>731327</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>673870</t>
+          <t>750506</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1518768</t>
+          <t>1409027</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1499311</t>
+          <t>1389789</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1539506</t>
+          <t>1422551</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,57 +4258,57 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>7932</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>3225</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>6960</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>37965</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,27 +4544,27 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>34389</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
